--- a/ConsolidadoResistenciaTeoricas.xlsx
+++ b/ConsolidadoResistenciaTeoricas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpulgarin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8EA6965-3CEC-44BD-AC0A-F0795D62FEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A4ABFA-CDDC-4ADB-B42A-891FE6644334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{D2C3D9F2-550D-4713-81E2-6CBF4CCD4D86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D2C3D9F2-550D-4713-81E2-6CBF4CCD4D86}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="10">
   <si>
     <t>TIPO</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Edad</t>
-  </si>
-  <si>
-    <t>PK</t>
   </si>
   <si>
     <t>Dato</t>
@@ -478,17 +475,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97642EC7-89A1-4FE3-B554-BCB8BEEE106C}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.5546875" style="4"/>
+    <col min="5" max="5" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -504,16 +501,13 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2">
         <v>21</v>
@@ -521,17 +515,16 @@
       <c r="D2" s="2">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2">
+      <c r="E2" s="2">
         <v>13.9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
         <v>21</v>
@@ -539,17 +532,16 @@
       <c r="D3" s="2">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="E3" s="2">
         <v>17.8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2">
         <v>21</v>
@@ -557,17 +549,16 @@
       <c r="D4" s="2">
         <v>28</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="E4" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2">
         <v>28</v>
@@ -575,17 +566,16 @@
       <c r="D5" s="2">
         <v>7</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="E5" s="2">
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
         <v>28</v>
@@ -593,17 +583,16 @@
       <c r="D6" s="2">
         <v>14</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="E6" s="2">
         <v>23.6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2">
         <v>28</v>
@@ -611,17 +600,16 @@
       <c r="D7" s="2">
         <v>28</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2">
         <v>34</v>
@@ -629,17 +617,16 @@
       <c r="D8" s="2">
         <v>7</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="E8" s="2">
         <v>22.4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2">
         <v>34</v>
@@ -647,17 +634,16 @@
       <c r="D9" s="2">
         <v>14</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="E9" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2">
         <v>34</v>
@@ -665,17 +651,16 @@
       <c r="D10" s="2">
         <v>28</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="E10" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2">
         <v>41</v>
@@ -683,17 +668,16 @@
       <c r="D11" s="2">
         <v>7</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="E11" s="2">
         <v>27.1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2">
         <v>41</v>
@@ -701,17 +685,16 @@
       <c r="D12" s="2">
         <v>14</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="E12" s="2">
         <v>34.6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2">
         <v>41</v>
@@ -719,17 +702,16 @@
       <c r="D13" s="2">
         <v>28</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
+      <c r="E13" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2">
         <v>48</v>
@@ -737,17 +719,16 @@
       <c r="D14" s="2">
         <v>7</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2">
+      <c r="E14" s="2">
         <v>31.7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2">
         <v>48</v>
@@ -755,17 +736,16 @@
       <c r="D15" s="2">
         <v>14</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2">
+      <c r="E15" s="2">
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2">
         <v>48</v>
@@ -773,17 +753,16 @@
       <c r="D16" s="2">
         <v>28</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="E16" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2">
         <v>21</v>
@@ -791,17 +770,16 @@
       <c r="D17" s="2">
         <v>7</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2">
+      <c r="E17" s="2">
         <v>13.9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2">
         <v>21</v>
@@ -809,17 +787,16 @@
       <c r="D18" s="2">
         <v>14</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2">
+      <c r="E18" s="2">
         <v>17.8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2">
         <v>21</v>
@@ -827,17 +804,16 @@
       <c r="D19" s="2">
         <v>28</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2">
+      <c r="E19" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2">
         <v>28</v>
@@ -845,17 +821,16 @@
       <c r="D20" s="2">
         <v>7</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2">
+      <c r="E20" s="2">
         <v>18.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2">
         <v>28</v>
@@ -863,17 +838,16 @@
       <c r="D21" s="2">
         <v>14</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2">
+      <c r="E21" s="2">
         <v>23.6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2">
         <v>28</v>
@@ -881,17 +855,16 @@
       <c r="D22" s="2">
         <v>28</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E22" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2">
         <v>34</v>
@@ -899,17 +872,16 @@
       <c r="D23" s="2">
         <v>7</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2">
+      <c r="E23" s="2">
         <v>22.4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2">
         <v>34</v>
@@ -917,17 +889,16 @@
       <c r="D24" s="2">
         <v>14</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2">
+      <c r="E24" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2">
         <v>34</v>
@@ -935,17 +906,16 @@
       <c r="D25" s="2">
         <v>28</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2">
+      <c r="E25" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2">
         <v>41</v>
@@ -953,17 +923,16 @@
       <c r="D26" s="2">
         <v>7</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2">
+      <c r="E26" s="2">
         <v>27.1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2">
         <v>41</v>
@@ -971,17 +940,16 @@
       <c r="D27" s="2">
         <v>14</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2">
+      <c r="E27" s="2">
         <v>34.6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2">
         <v>41</v>
@@ -989,17 +957,16 @@
       <c r="D28" s="2">
         <v>28</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2">
+      <c r="E28" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2">
         <v>48</v>
@@ -1007,17 +974,16 @@
       <c r="D29" s="2">
         <v>7</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2">
+      <c r="E29" s="2">
         <v>31.7</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2">
         <v>48</v>
@@ -1025,17 +991,16 @@
       <c r="D30" s="2">
         <v>14</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2">
+      <c r="E30" s="2">
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2">
         <v>48</v>
@@ -1043,17 +1008,16 @@
       <c r="D31" s="2">
         <v>28</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2">
+      <c r="E31" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2">
         <v>28</v>
@@ -1061,17 +1025,16 @@
       <c r="D32" s="2">
         <v>7</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2">
+      <c r="E32" s="2">
         <v>18.5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2">
         <v>28</v>
@@ -1079,17 +1042,16 @@
       <c r="D33" s="2">
         <v>14</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2">
+      <c r="E33" s="2">
         <v>23.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2">
         <v>28</v>
@@ -1097,17 +1059,16 @@
       <c r="D34" s="2">
         <v>28</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E34" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="2">
         <v>34</v>
@@ -1115,17 +1076,16 @@
       <c r="D35" s="2">
         <v>7</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2">
+      <c r="E35" s="2">
         <v>22.4</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2">
         <v>34</v>
@@ -1133,17 +1093,16 @@
       <c r="D36" s="2">
         <v>14</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2">
+      <c r="E36" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" s="2">
         <v>34</v>
@@ -1151,17 +1110,16 @@
       <c r="D37" s="2">
         <v>28</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2">
+      <c r="E37" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="2">
         <v>41</v>
@@ -1169,17 +1127,16 @@
       <c r="D38" s="2">
         <v>7</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2">
+      <c r="E38" s="2">
         <v>27.1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="2">
         <v>41</v>
@@ -1187,17 +1144,16 @@
       <c r="D39" s="2">
         <v>14</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2">
+      <c r="E39" s="2">
         <v>34.6</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" s="2">
         <v>41</v>
@@ -1205,17 +1161,16 @@
       <c r="D40" s="2">
         <v>28</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2">
+      <c r="E40" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" s="2">
         <v>48</v>
@@ -1223,17 +1178,16 @@
       <c r="D41" s="2">
         <v>7</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2">
+      <c r="E41" s="2">
         <v>31.7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" s="2">
         <v>48</v>
@@ -1241,17 +1195,16 @@
       <c r="D42" s="2">
         <v>14</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2">
+      <c r="E42" s="2">
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="2">
         <v>48</v>
@@ -1259,17 +1212,16 @@
       <c r="D43" s="2">
         <v>28</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2">
+      <c r="E43" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="2">
         <v>21</v>
@@ -1277,17 +1229,16 @@
       <c r="D44" s="2">
         <v>7</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2">
+      <c r="E44" s="2">
         <v>11.8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="2">
         <v>21</v>
@@ -1295,17 +1246,16 @@
       <c r="D45" s="2">
         <v>14</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2">
+      <c r="E45" s="2">
         <v>16.5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" s="2">
         <v>21</v>
@@ -1313,17 +1263,16 @@
       <c r="D46" s="2">
         <v>28</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2">
+      <c r="E46" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="2">
         <v>28</v>
@@ -1331,17 +1280,16 @@
       <c r="D47" s="2">
         <v>7</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2">
+      <c r="E47" s="2">
         <v>15.7</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="2">
         <v>28</v>
@@ -1349,17 +1297,16 @@
       <c r="D48" s="2">
         <v>14</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2">
+      <c r="E48" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" s="2">
         <v>28</v>
@@ -1367,8 +1314,7 @@
       <c r="D49" s="2">
         <v>28</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2">
+      <c r="E49" s="2">
         <v>28</v>
       </c>
     </row>
